--- a/custom_env/skill_util/Haoqiang/Select.xlsx
+++ b/custom_env/skill_util/Haoqiang/Select.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanwu/Downloads/Export/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7B0C744-6AC1-B348-ADB6-3A7CB19A1DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AB0622-9A11-8F42-8922-D69187E2199F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36820" yWindow="6540" windowWidth="31380" windowHeight="19440" xr2:uid="{AD22497F-B2E6-8F40-9BB8-69F05F378A37}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="267">
   <si>
     <t>Folder Name</t>
   </si>
@@ -810,6 +810,33 @@
   </si>
   <si>
     <t>0.38u</t>
+  </si>
+  <si>
+    <t>tmp_20240911093227382367289_tt</t>
+  </si>
+  <si>
+    <t>16.0p</t>
+  </si>
+  <si>
+    <t>2.3p</t>
+  </si>
+  <si>
+    <t>14.0f</t>
+  </si>
+  <si>
+    <t>3.7k</t>
+  </si>
+  <si>
+    <t>0.58u</t>
+  </si>
+  <si>
+    <t>1.16u</t>
+  </si>
+  <si>
+    <t>0.36u</t>
+  </si>
+  <si>
+    <t>0.34u</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9F3436-B45B-4D4D-BAF8-C5F2D64BCD5D}">
-  <dimension ref="A1:FT5"/>
+  <dimension ref="A1:FT6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:176">
@@ -3847,6 +3874,536 @@
       </c>
       <c r="FT5">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:176">
+      <c r="A6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6">
+        <v>-0.46325708700000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.9786899999999999E-6</v>
+      </c>
+      <c r="E6">
+        <v>3.9387759999999997E-3</v>
+      </c>
+      <c r="F6">
+        <v>35.825899999999997</v>
+      </c>
+      <c r="G6">
+        <v>115853.6</v>
+      </c>
+      <c r="H6">
+        <v>65.037540000000007</v>
+      </c>
+      <c r="I6">
+        <v>169281.3</v>
+      </c>
+      <c r="J6">
+        <v>66.686959999999999</v>
+      </c>
+      <c r="K6">
+        <v>162248.5</v>
+      </c>
+      <c r="L6">
+        <v>49.038020000000003</v>
+      </c>
+      <c r="M6">
+        <v>18436890</v>
+      </c>
+      <c r="N6">
+        <v>78.304339999999996</v>
+      </c>
+      <c r="O6">
+        <v>21518670</v>
+      </c>
+      <c r="P6">
+        <v>78.769779999999997</v>
+      </c>
+      <c r="Q6">
+        <v>19759110</v>
+      </c>
+      <c r="R6">
+        <v>78.215400000000002</v>
+      </c>
+      <c r="S6">
+        <v>952015.5</v>
+      </c>
+      <c r="T6">
+        <v>0.16747699999999999</v>
+      </c>
+      <c r="U6">
+        <v>0.21182599999999999</v>
+      </c>
+      <c r="V6">
+        <v>67.473150959999998</v>
+      </c>
+      <c r="W6">
+        <v>67.466361329999998</v>
+      </c>
+      <c r="X6">
+        <v>39.68748411</v>
+      </c>
+      <c r="Y6">
+        <v>15.62637003</v>
+      </c>
+      <c r="Z6">
+        <v>6.9100270090000002</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>260</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>261</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>262</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>189</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL6">
+        <v>5</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AU6">
+        <v>5</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>216</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>194</v>
+      </c>
+      <c r="AX6">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>216</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>194</v>
+      </c>
+      <c r="BA6">
+        <v>10</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>199</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>200</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>199</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>200</v>
+      </c>
+      <c r="BG6">
+        <v>1</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>216</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>201</v>
+      </c>
+      <c r="BJ6">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>198</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>194</v>
+      </c>
+      <c r="BM6">
+        <v>3</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>257</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>213</v>
+      </c>
+      <c r="BP6">
+        <v>4</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>193</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>263</v>
+      </c>
+      <c r="BS6">
+        <v>4</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>189</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>189</v>
+      </c>
+      <c r="BV6">
+        <v>10</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>189</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>230</v>
+      </c>
+      <c r="BY6">
+        <v>3</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>189</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>230</v>
+      </c>
+      <c r="CB6">
+        <v>3</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>200</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>193</v>
+      </c>
+      <c r="CE6">
+        <v>1</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>189</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>189</v>
+      </c>
+      <c r="CH6">
+        <v>10</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>200</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>193</v>
+      </c>
+      <c r="CK6">
+        <v>10</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>192</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>222</v>
+      </c>
+      <c r="CN6">
+        <v>1</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>215</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>200</v>
+      </c>
+      <c r="CQ6">
+        <v>1</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>215</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>200</v>
+      </c>
+      <c r="CT6">
+        <v>2</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>215</v>
+      </c>
+      <c r="CV6" t="s">
+        <v>200</v>
+      </c>
+      <c r="CW6">
+        <v>4</v>
+      </c>
+      <c r="CX6" t="s">
+        <v>215</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>200</v>
+      </c>
+      <c r="CZ6">
+        <v>3</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>199</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>239</v>
+      </c>
+      <c r="DC6">
+        <v>5</v>
+      </c>
+      <c r="DD6" t="s">
+        <v>199</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>239</v>
+      </c>
+      <c r="DF6">
+        <v>5</v>
+      </c>
+      <c r="DG6" t="s">
+        <v>192</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>222</v>
+      </c>
+      <c r="DI6">
+        <v>3</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>192</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>222</v>
+      </c>
+      <c r="DL6">
+        <v>1</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>192</v>
+      </c>
+      <c r="DN6" t="s">
+        <v>222</v>
+      </c>
+      <c r="DO6">
+        <v>10</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>192</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>222</v>
+      </c>
+      <c r="DR6">
+        <v>10</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>199</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>202</v>
+      </c>
+      <c r="DU6">
+        <v>5</v>
+      </c>
+      <c r="DV6" t="s">
+        <v>192</v>
+      </c>
+      <c r="DW6" t="s">
+        <v>222</v>
+      </c>
+      <c r="DX6">
+        <v>3</v>
+      </c>
+      <c r="DY6" t="s">
+        <v>215</v>
+      </c>
+      <c r="DZ6" t="s">
+        <v>264</v>
+      </c>
+      <c r="EA6">
+        <v>4</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>192</v>
+      </c>
+      <c r="EC6" t="s">
+        <v>222</v>
+      </c>
+      <c r="ED6">
+        <v>1</v>
+      </c>
+      <c r="EE6" t="s">
+        <v>192</v>
+      </c>
+      <c r="EF6" t="s">
+        <v>222</v>
+      </c>
+      <c r="EG6">
+        <v>10</v>
+      </c>
+      <c r="EH6" t="s">
+        <v>190</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>199</v>
+      </c>
+      <c r="EJ6">
+        <v>4</v>
+      </c>
+      <c r="EK6" t="s">
+        <v>190</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>199</v>
+      </c>
+      <c r="EM6">
+        <v>4</v>
+      </c>
+      <c r="EN6" t="s">
+        <v>190</v>
+      </c>
+      <c r="EO6" t="s">
+        <v>192</v>
+      </c>
+      <c r="EP6">
+        <v>5</v>
+      </c>
+      <c r="EQ6" t="s">
+        <v>189</v>
+      </c>
+      <c r="ER6" t="s">
+        <v>198</v>
+      </c>
+      <c r="ES6">
+        <v>2</v>
+      </c>
+      <c r="ET6" t="s">
+        <v>190</v>
+      </c>
+      <c r="EU6" t="s">
+        <v>192</v>
+      </c>
+      <c r="EV6">
+        <v>2</v>
+      </c>
+      <c r="EW6" t="s">
+        <v>189</v>
+      </c>
+      <c r="EX6" t="s">
+        <v>194</v>
+      </c>
+      <c r="EY6">
+        <v>9</v>
+      </c>
+      <c r="EZ6" t="s">
+        <v>189</v>
+      </c>
+      <c r="FA6" t="s">
+        <v>194</v>
+      </c>
+      <c r="FB6">
+        <v>6</v>
+      </c>
+      <c r="FC6" t="s">
+        <v>190</v>
+      </c>
+      <c r="FD6" t="s">
+        <v>201</v>
+      </c>
+      <c r="FE6">
+        <v>1</v>
+      </c>
+      <c r="FF6" t="s">
+        <v>190</v>
+      </c>
+      <c r="FG6" t="s">
+        <v>201</v>
+      </c>
+      <c r="FH6">
+        <v>1</v>
+      </c>
+      <c r="FI6" t="s">
+        <v>265</v>
+      </c>
+      <c r="FJ6" t="s">
+        <v>266</v>
+      </c>
+      <c r="FK6">
+        <v>5</v>
+      </c>
+      <c r="FL6" t="s">
+        <v>199</v>
+      </c>
+      <c r="FM6" t="s">
+        <v>192</v>
+      </c>
+      <c r="FN6">
+        <v>3</v>
+      </c>
+      <c r="FO6" t="s">
+        <v>199</v>
+      </c>
+      <c r="FP6" t="s">
+        <v>192</v>
+      </c>
+      <c r="FQ6">
+        <v>3</v>
+      </c>
+      <c r="FR6" t="s">
+        <v>189</v>
+      </c>
+      <c r="FS6" t="s">
+        <v>194</v>
+      </c>
+      <c r="FT6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
